--- a/assets/docs/plazas.xlsx
+++ b/assets/docs/plazas.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8A9F9C-3CDE-4B7C-AE36-FBA5D7620CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29935CD9-B615-4732-9B96-436BF6B80589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
+    <workbookView xWindow="-108" yWindow="252" windowWidth="23256" windowHeight="11952" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
   </bookViews>
   <sheets>
     <sheet name="Plazas" sheetId="1" r:id="rId1"/>
+    <sheet name="CATEGORIA" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>PUESTO</t>
   </si>
@@ -44,13 +45,34 @@
   </si>
   <si>
     <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>CONFIANZA</t>
+  </si>
+  <si>
+    <t>HONORARIOS</t>
+  </si>
+  <si>
+    <t>EVENTUAL</t>
+  </si>
+  <si>
+    <t>SINDICALIZADO</t>
+  </si>
+  <si>
+    <t>BASE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +84,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -90,14 +119,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -410,29 +458,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF703789-3435-4D03-ABEF-93E46EBDB414}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" style="3"/>
+    <col min="2" max="2" width="19.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="4"/>
+    <col min="5" max="16384" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{C8FD7146-5F94-422D-99DF-F95CF58DABB4}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{A70BD037-198D-4B95-86FD-0EAFD2AEABF6}">
+      <formula1>0</formula1>
+      <formula2>365</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{44BE119F-A353-4A8A-92A8-D9B5C320664A}">
+          <x14:formula1>
+            <xm:f>CATEGORIA!$A$1:$A$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA55D9E-52B6-4DB3-8A66-045D0C2B8DA5}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/docs/plazas.xlsx
+++ b/assets/docs/plazas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29935CD9-B615-4732-9B96-436BF6B80589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AFEBAB-A7EF-4BB4-8A6A-316B1D21C756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="252" windowWidth="23256" windowHeight="11952" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
   </bookViews>
   <sheets>
     <sheet name="Plazas" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>PUESTO</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>BASE</t>
+  </si>
+  <si>
+    <t>DIETAS</t>
   </si>
 </sst>
 </file>
@@ -502,7 +505,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{44BE119F-A353-4A8A-92A8-D9B5C320664A}">
           <x14:formula1>
-            <xm:f>CATEGORIA!$A$1:$A$5</xm:f>
+            <xm:f>CATEGORIA!$A$1:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>E1:E1048576</xm:sqref>
         </x14:dataValidation>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA55D9E-52B6-4DB3-8A66-045D0C2B8DA5}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
@@ -545,6 +548,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/docs/plazas.xlsx
+++ b/assets/docs/plazas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\cnomina\assets\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AFEBAB-A7EF-4BB4-8A6A-316B1D21C756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B96859F-0FB0-4E28-9630-030F07E94E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{A93F2C7B-DD2B-4A17-ABE6-6D97DDF9E267}"/>
   </bookViews>
@@ -468,7 +468,8 @@
     <col min="2" max="2" width="19.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" style="4"/>
-    <col min="5" max="16384" width="11.5546875" style="3"/>
+    <col min="5" max="5" width="15.109375" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="11.5546875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
